--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-device.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Device</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Device|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -431,7 +431,7 @@
     <t>Device.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -469,7 +469,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -527,7 +527,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -649,7 +649,7 @@
     <t>Device.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DeviceDefinition)
+    <t xml:space="preserve">Reference(DeviceDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -897,7 +897,7 @@
     <t>デバイスの可用性ステータス理由。 / The availability status reason of the device.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1079,7 +1079,7 @@
     <t>医療機器を識別するコード。 / Codes to identify medical devices.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-type</t>
+    <t>http://hl7.org/fhir/ValueSet/device-type|4.0.1</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1215,7 +1215,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient)
+    <t xml:space="preserve">Reference(Patient|4.0.1)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -1275,7 +1275,7 @@
     <t>Device.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1337,7 +1337,7 @@
     <t>Device.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1674,7 +1674,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1689,7 +1689,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.0703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="40.71484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-device.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Device|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Device</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -431,7 +431,7 @@
     <t>Device.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
@@ -469,7 +469,7 @@
     <t>医療プライバシーおよびセキュリティ分類システムからのセキュリティラベル。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -527,7 +527,7 @@
     <t>人間の言語。 / A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -649,7 +649,7 @@
     <t>Device.definition</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DeviceDefinition|4.0.1)
+    <t xml:space="preserve">Reference(DeviceDefinition)
 </t>
   </si>
   <si>
@@ -897,7 +897,7 @@
     <t>デバイスの可用性ステータス理由。 / The availability status reason of the device.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/device-status-reason</t>
   </si>
   <si>
     <t>Device.distinctIdentifier</t>
@@ -1079,7 +1079,7 @@
     <t>医療機器を識別するコード。 / Codes to identify medical devices.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/device-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/device-type</t>
   </si>
   <si>
     <t>Device.specialization</t>
@@ -1215,7 +1215,7 @@
     <t>Device.patient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1)
+    <t xml:space="preserve">Reference(Patient)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>Device.owner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -1275,7 +1275,7 @@
     <t>Device.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
+    <t xml:space="preserve">Reference(Location)
 </t>
   </si>
   <si>
@@ -1337,7 +1337,7 @@
     <t>Device.parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(Device)
 </t>
   </si>
   <si>
@@ -1674,7 +1674,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="29.08984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="24.5625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1689,7 +1689,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.0703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="40.71484375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.10546875" customWidth="true" bestFit="true"/>
